--- a/src/test/resources/testdata/Modules/02_ClaimPoints/ClaimPoints/03_CategoryPageTest.xlsx
+++ b/src/test/resources/testdata/Modules/02_ClaimPoints/ClaimPoints/03_CategoryPageTest.xlsx
@@ -1,26 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\02_ClaimPoints\ClaimPoints\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3FEC1B6-C1FD-49D2-88E1-7B300A0FCEB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAFDC4B0-5AC9-4846-A51A-2A2061B0CFB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D5674106-8292-4F40-9DFC-E6EAC771FC2F}"/>
   </bookViews>
   <sheets>
     <sheet name="TestCases" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="127">
   <si>
     <t>TESTCASE_ID</t>
   </si>
@@ -217,8 +231,155 @@
     </r>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Verify after </t>
+    <t>CategoryPageTest_02</t>
+  </si>
+  <si>
+    <t>CategoryPageTest_03</t>
+  </si>
+  <si>
+    <t>CategoryPageTest_04</t>
+  </si>
+  <si>
+    <t>CategoryPageTest_05</t>
+  </si>
+  <si>
+    <t>CategoryPageTest_06</t>
+  </si>
+  <si>
+    <t>CategoryPageTest_07</t>
+  </si>
+  <si>
+    <t>CategoryPageTest_08</t>
+  </si>
+  <si>
+    <t>CategoryPageTest_09</t>
+  </si>
+  <si>
+    <t>CategoryPageTest_10</t>
+  </si>
+  <si>
+    <t>CategoryPageTest_11</t>
+  </si>
+  <si>
+    <t>CategoryPageTest_12</t>
+  </si>
+  <si>
+    <t>CategoryPageTest_13</t>
+  </si>
+  <si>
+    <t>Verify added Product Qty on cartDetails page</t>
+  </si>
+  <si>
+    <t>Verify Total Claims Points  on cart Details page</t>
+  </si>
+  <si>
+    <t>Verify added Product Total Points on cart Details page</t>
+  </si>
+  <si>
+    <t>Verify added Product Code &amp; name on cart Details page</t>
+  </si>
+  <si>
+    <t>Verify on cart Details page after click on Plus button then qty should be add</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify on cart Details page after click on minus button then qty should be minus </t>
+  </si>
+  <si>
+    <t>Verify on cart  Detailspage after click on Back arrow Cancel claim popup should be display</t>
+  </si>
+  <si>
+    <t>Verify on cart Detailspage after click on cancel button  Cancel claim popup should be display</t>
+  </si>
+  <si>
+    <t>Verify on cart Details page after click on Delete button  Delete claim popup should be display</t>
+  </si>
+  <si>
+    <t>Verify on cart Details page after delete product product should not be show on cart details page</t>
+  </si>
+  <si>
+    <t>Verify on cart Details page is empty then submit button should be disable.</t>
+  </si>
+  <si>
+    <t>CategoryPageTest_14</t>
+  </si>
+  <si>
+    <t>CategoryPageTest_15</t>
+  </si>
+  <si>
+    <t>CategoryPageTest_16</t>
+  </si>
+  <si>
+    <t>CategoryPageTest_17</t>
+  </si>
+  <si>
+    <t>CategoryPageTest_18</t>
+  </si>
+  <si>
+    <t>CategoryPageTest_19</t>
+  </si>
+  <si>
+    <t>CategoryPageTest_20</t>
+  </si>
+  <si>
+    <t>CategoryPageTest_21</t>
+  </si>
+  <si>
+    <t>CategoryPageTest_22</t>
+  </si>
+  <si>
+    <t>CategoryPageTest_23</t>
+  </si>
+  <si>
+    <t>CategoryPageTest_24</t>
+  </si>
+  <si>
+    <t>CategoryPageTest_25</t>
+  </si>
+  <si>
+    <t>CategoryPageTest_26</t>
+  </si>
+  <si>
+    <t>CategoryPageTest_27</t>
+  </si>
+  <si>
+    <t>CategoryPageTest_28</t>
+  </si>
+  <si>
+    <t>Verify After click on cart details page submit button user should navigate to Claim Information page.</t>
+  </si>
+  <si>
+    <t>2602000005</t>
+  </si>
+  <si>
+    <t>02_ClaimPoints</t>
+  </si>
+  <si>
+    <t>CATEGORY_NAME</t>
+  </si>
+  <si>
+    <t>BRAND_NAME</t>
+  </si>
+  <si>
+    <t>TMT</t>
+  </si>
+  <si>
+    <t>INV_NO</t>
+  </si>
+  <si>
+    <t>INV001_</t>
+  </si>
+  <si>
+    <t>PRODUCT_NAME</t>
+  </si>
+  <si>
+    <t>QTY</t>
+  </si>
+  <si>
+    <t>UOM</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">After </t>
     </r>
     <r>
       <rPr>
@@ -250,17 +411,17 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Refresh</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> icon </t>
+      <t>category,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
@@ -271,276 +432,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>page should be refresh</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <t>Verify Search field by Invalid data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify after clear search field all records should be show pn page </t>
-  </si>
-  <si>
-    <t>Verify Search field by valid data.</t>
-  </si>
-  <si>
-    <t>CategoryPageTest_02</t>
-  </si>
-  <si>
-    <t>CategoryPageTest_03</t>
-  </si>
-  <si>
-    <t>CategoryPageTest_04</t>
-  </si>
-  <si>
-    <t>CategoryPageTest_05</t>
-  </si>
-  <si>
-    <t>CategoryPageTest_06</t>
-  </si>
-  <si>
-    <t>CategoryPageTest_07</t>
-  </si>
-  <si>
-    <t>Verify if qty field is blank &amp; if click on Add to cart button then warning msg should be show.</t>
-  </si>
-  <si>
-    <t>Add  products in cart &amp; verify Product count on  cart icon.</t>
-  </si>
-  <si>
-    <t>Verify Points calculation on category page</t>
-  </si>
-  <si>
-    <t>Verify UOM conversion on categoty page.</t>
-  </si>
-  <si>
-    <t>CategoryPageTest_08</t>
-  </si>
-  <si>
-    <t>CategoryPageTest_09</t>
-  </si>
-  <si>
-    <t>CategoryPageTest_10</t>
-  </si>
-  <si>
-    <t>CategoryPageTest_11</t>
-  </si>
-  <si>
-    <t>Verify if we add same product for different parameter combination then it should be add. (ex. Product 1 with diamer 10  &amp; Product 1 with diameter 20) then 2 products should be add In cart.</t>
-  </si>
-  <si>
-    <t>Verify if we add same product with same parameter then in cart only 1 product should show with latest added values.</t>
-  </si>
-  <si>
-    <t>CategoryPageTest_12</t>
-  </si>
-  <si>
-    <t>CategoryPageTest_13</t>
-  </si>
-  <si>
-    <t>Verify KG UOM should be only accept Integer value</t>
-  </si>
-  <si>
-    <t>Verify Tonne UOM should be  accept decimal value</t>
-  </si>
-  <si>
-    <t>Verify Quintal UOM should be  accept decimal value</t>
-  </si>
-  <si>
-    <t>Verify On cart page Prodcuts should be show category wise.</t>
-  </si>
-  <si>
-    <t>Verify added Product Qty on cartDetails page</t>
-  </si>
-  <si>
-    <t>Verify Total Claims Points  on cart Details page</t>
-  </si>
-  <si>
-    <t>Verify added Product Total Points on cart Details page</t>
-  </si>
-  <si>
-    <t>Verify added Product Points on cart Details page</t>
-  </si>
-  <si>
-    <t>Verify added ProductUOM  on cart Details page</t>
-  </si>
-  <si>
-    <t>Verify added Product Code &amp; name on cart Details page</t>
-  </si>
-  <si>
-    <t>verify product Count on cart Details  page</t>
-  </si>
-  <si>
-    <t>Verify added product category on cart Details page</t>
-  </si>
-  <si>
-    <t>Verify after click on cart icon navigate to cart Details page</t>
-  </si>
-  <si>
-    <t>Verify on cart Details page after click on Plus button then qty should be add</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify on cart Details page after click on minus button then qty should be minus </t>
-  </si>
-  <si>
-    <t>Verify on cart  Detailspage after click on Back arrow Cancel claim popup should be display</t>
-  </si>
-  <si>
-    <t>Verify on cart Detailspage after click on cancel button  Cancel claim popup should be display</t>
-  </si>
-  <si>
-    <t>Verify on cart Details page after click on Delete button  Delete claim popup should be display</t>
-  </si>
-  <si>
-    <t>Verify on cart Details page after delete product product should not be show on cart details page</t>
-  </si>
-  <si>
-    <t>Verify on cart Details page is empty then submit button should be disable.</t>
-  </si>
-  <si>
-    <t>Verify on cart Details page if click on cancel claim pop-up Yes button then navigate to category page.</t>
-  </si>
-  <si>
-    <t>CategoryPageTest_14</t>
-  </si>
-  <si>
-    <t>CategoryPageTest_15</t>
-  </si>
-  <si>
-    <t>CategoryPageTest_16</t>
-  </si>
-  <si>
-    <t>CategoryPageTest_17</t>
-  </si>
-  <si>
-    <t>CategoryPageTest_18</t>
-  </si>
-  <si>
-    <t>CategoryPageTest_19</t>
-  </si>
-  <si>
-    <t>CategoryPageTest_20</t>
-  </si>
-  <si>
-    <t>CategoryPageTest_21</t>
-  </si>
-  <si>
-    <t>CategoryPageTest_22</t>
-  </si>
-  <si>
-    <t>CategoryPageTest_23</t>
-  </si>
-  <si>
-    <t>CategoryPageTest_24</t>
-  </si>
-  <si>
-    <t>CategoryPageTest_25</t>
-  </si>
-  <si>
-    <t>CategoryPageTest_26</t>
-  </si>
-  <si>
-    <t>CategoryPageTest_27</t>
-  </si>
-  <si>
-    <t>CategoryPageTest_28</t>
-  </si>
-  <si>
-    <t>CategoryPageTest_29</t>
-  </si>
-  <si>
-    <t>CategoryPageTest_30</t>
-  </si>
-  <si>
-    <t>CategoryPageTest_31</t>
-  </si>
-  <si>
-    <t>CategoryPageTest_32</t>
-  </si>
-  <si>
-    <t>CategoryPageTest_33</t>
-  </si>
-  <si>
-    <t>CategoryPageTest_34</t>
-  </si>
-  <si>
-    <t>CategoryPageTest_35</t>
-  </si>
-  <si>
-    <t>Verify After click on cart details page submit button user should navigate to Claim Information page.</t>
-  </si>
-  <si>
-    <t>2602000005</t>
-  </si>
-  <si>
-    <t>02_ClaimPoints</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">After </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>click</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> on </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>category</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>brand</t>
+      <t>brands</t>
     </r>
     <r>
       <rPr>
@@ -552,15 +444,6 @@
       </rPr>
       <t xml:space="preserve"> should be display.</t>
     </r>
-  </si>
-  <si>
-    <t>CATEGORY_NAME</t>
-  </si>
-  <si>
-    <t>BRAND_NAME</t>
-  </si>
-  <si>
-    <t>TMT</t>
   </si>
   <si>
     <t>openclaimpointsmenu
@@ -571,7 +454,765 @@
 clickonbrowsefileoption
 selectimageclickonbrowsefileoption
 dealer_clickonnextbutton
-category_selectcategory</t>
+category_selectcategory
+verify_category_cartandrefrshicon_isdisplay</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Verify after click on </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Refresh icon</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> , </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>page</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> should be </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>refresh</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>category_clickon_refreshbtn
+verify_category_brandscontainer_isdisplayed</t>
+  </si>
+  <si>
+    <t>true</t>
+  </si>
+  <si>
+    <t>false</t>
+  </si>
+  <si>
+    <t>category_clickon_carticon
+verify_category_get_warningtoastmsg</t>
+  </si>
+  <si>
+    <t>Add quantity to atleast one product</t>
+  </si>
+  <si>
+    <t>category_selectcategory
+verify_category_brandscontainer_isdisplayed</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Verify </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Search field</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> by </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Invalid</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> data</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Verify afte</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>r clear search field, all records</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> should be show pn page </t>
+    </r>
+  </si>
+  <si>
+    <t>Jindal Panther</t>
+  </si>
+  <si>
+    <t>roundds</t>
+  </si>
+  <si>
+    <t>No data available</t>
+  </si>
+  <si>
+    <t>category_selectbrand
+category_enterproductname_insearchfield
+hidekeyboard
+verify_category_get_warningtoastmsg</t>
+  </si>
+  <si>
+    <t>category_enterproductname_insearchfield
+hidekeyboard
+verify_category_productsinlist_isdisplayed</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Verify </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Search</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> field by </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>valid</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> data.</t>
+    </r>
+  </si>
+  <si>
+    <t>category_enterproductname_insearchfield
+hidekeyboard
+verify_category_productcode_inlist</t>
+  </si>
+  <si>
+    <t>PROD005</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Verify if </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>qty field is blank</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; if click on Add to cart button then</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> warning msg</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> should be show.</t>
+    </r>
+  </si>
+  <si>
+    <t>Cement</t>
+  </si>
+  <si>
+    <t>Ambuja Cement</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Verify </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Points calculation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> on category page</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Verify </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>UOM conversion</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> on categoty page.</t>
+    </r>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>0.005</t>
+  </si>
+  <si>
+    <t>category_enterqty
+hidekeyboard
+verify_category_tonne_uom</t>
+  </si>
+  <si>
+    <t>category_clear_searchfield
+category_clickon_refreshbtn
+category_selectcategory
+category_selectbrand
+category_clickon_addtocart_btn
+verify_category_get_qtywarningtoastmsg</t>
+  </si>
+  <si>
+    <t>category_clickon_refreshbtn
+category_selectcategory
+category_selectbrand
+category_enterqty
+hidekeyboard
+category_get_totalpoints_fieldvalue
+verify_category_totalpoints_fieldvalue</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Verify if we </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>add same produc</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">t for </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>different parameter</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> combination then it should be </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>add</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. (ex. Product 1 with diamer 10  &amp; Product 1 with diameter 20) then 2 products should be add In cart.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Verify if we </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>add same product</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> with </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>same parameter</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> then in cart </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>only 1 product</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> should show with </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>latest added values</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>PRODUCT_REMARK</t>
+  </si>
+  <si>
+    <t>ProductAdded</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Verify added </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>product category</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> on </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>cart Details</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> page</t>
+    </r>
+  </si>
+  <si>
+    <t>category_enterqty
+hidekeyboard
+category_clickon_addtocart_btn
+category_enter_secondqty
+hidekeyboard
+category_clickon_addtocart_btn
+category_clickon_carticon
+verify_cartdetails_productcount</t>
+  </si>
+  <si>
+    <t>verify_cartdetails_added_categoryname
+cartdetails_clickon_cancelbtn
+cartdetails_clickon_alertbox_yesbtn</t>
+  </si>
+  <si>
+    <t>category_clickon_refreshbtn
+category_selectcategory
+category_selectbrand
+category_enterqty
+hidekeyboard
+category_enter_productremark
+hidekeyboard
+category_clickon_addtocart_btn
+category_enterqty
+hidekeyboard
+category_enter_productremark
+hidekeyboard
+category_clickon_addtocart_btn
+category_clickon_carticon
+verify_cartdetails_productcount
+cartdetails_clickon_cancelbtn
+cartdetails_clickon_alertbox_yesbtn</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>verify_cartdetails_productdescription</t>
+  </si>
+  <si>
+    <t>Verify added Product name/Descrpition  on cart Details page</t>
+  </si>
+  <si>
+    <t>Verify added Product UOM  on cart Details page</t>
+  </si>
+  <si>
+    <t>verify_cartdetails_uom</t>
+  </si>
+  <si>
+    <t>category_clickon_refreshbtn
+category_selectcategory
+category_selectbrand
+category_productcode_inlist
+category_productdesc_inlist
+category_productuom_inlist
+category_enterqty
+hidekeyboard
+category_get_totalpoints_fieldvalue
+category_clickon_addtocart_btn
+category_clickon_carticon
+cartdetails_clickon_updownarrow
+verify_cartdetails_productcode</t>
+  </si>
+  <si>
+    <t>verify_cartdetails_totalpoints</t>
+  </si>
+  <si>
+    <t>verify_cartdetails_qty</t>
+  </si>
+  <si>
+    <t>Ambj001:12,Ambo002:10</t>
+  </si>
+  <si>
+    <t>cartdetails_clickon_cancelbtn
+cartdetails_clickon_alertbox_yesbtn
+category_addproductsincart
+category_clickon_carticon
+cartdetails_clickon_updownarrow
+cartdetails_get_additionoftotalpoints
+verify_cartdetails_totalclaimpoints</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>cartdetails_clickon_minusicon
+verify_cartdetails_minusqty</t>
+  </si>
+  <si>
+    <t>Cancel Claim</t>
+  </si>
+  <si>
+    <t>Delete Claim</t>
+  </si>
+  <si>
+    <t>clickonbackarrow
+verify_cartdetails_alertbox_title
+cartdetails_clickon_alertbox_nobtn</t>
+  </si>
+  <si>
+    <t>cartdetails_clickon_cancelbtn
+verify_cartdetails_alertbox_title</t>
+  </si>
+  <si>
+    <t>Verify on cart Details page if click on cancel claim pop-up yes button then navigate to category page.</t>
+  </si>
+  <si>
+    <t>cartdetails_clickon_alertbox_yesbtn
+verifypagetitle</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>category_enterqty
+hidekeyboard
+category_clickon_addtocart_btn
+category_clickon_carticon
+cartdetails_clickon_updownarrow
+cartdetails_clickon_deleteicon
+verify_cartdetails_alertbox_title</t>
+  </si>
+  <si>
+    <t>cartdetails_clickon_alertbox_nobtn
+cartdetails_clickon_deleteicon
+cartdetails_clickon_alertbox_yesbtn
+verify_cartdetails_nodatafoundtext</t>
+  </si>
+  <si>
+    <t>Data Not Available</t>
+  </si>
+  <si>
+    <t>verify_cartdetails_submitbtn_isenabled</t>
+  </si>
+  <si>
+    <t>Claim Information</t>
+  </si>
+  <si>
+    <t>cartdetails_clickon_cancelbtn
+cartdetails_clickon_alertbox_yesbtn
+category_enterqty
+hidekeyboard
+category_clickon_addtocart_btn
+category_clickon_carticon
+cartdetails_clickon_submitbtn
+verifypagetitle
+clickonbackarrow
+cartdetails_clickon_cancelbtn
+cartdetails_clickon_alertbox_yesbtn
+clickonbackarrow
+dealerlist_clickoncrossicon
+navigatebacktodashboardpage</t>
+  </si>
+  <si>
+    <t>cartdetails_clickon_cancelbtn
+cartdetails_clickon_alertbox_yesbtn
+category_clear_searchfield
+category_enterqty
+hidekeyboard
+category_clickon_addtocart_btn
+category_clickon_carticon
+cartdetails_clickon_updownarrow
+verify_cartdetails_addqty</t>
+  </si>
+  <si>
+    <t>10</t>
   </si>
 </sst>
 </file>
@@ -733,7 +1374,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -916,6 +1557,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF0070C0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1120,7 +1767,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1131,6 +1778,17 @@
     <xf numFmtId="49" fontId="13" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="13" fillId="33" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="13" fillId="33" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1507,20 +2165,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{089D5808-B2AF-4105-BEF8-05FAA4CBE122}">
-  <dimension ref="A1:I36"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:N29"/>
+  <sheetFormatPr defaultColWidth="12.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="20.90625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.453125" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="152.08984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="37.6328125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="24.08984375" style="2" customWidth="1"/>
-    <col min="9" max="9" width="11.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.90625" style="2"/>
+    <col min="1" max="2" width="12.1796875" style="2"/>
+    <col min="3" max="3" width="18.54296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.1796875" style="2"/>
+    <col min="5" max="5" width="50.08984375" style="2" customWidth="1"/>
+    <col min="6" max="7" width="12.1796875" style="2"/>
+    <col min="8" max="8" width="13.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.453125" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="12.1796875" style="2"/>
+    <col min="12" max="12" width="17.08984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="12.1796875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>6</v>
       </c>
@@ -1537,24 +2197,39 @@
         <v>3</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="H1" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="M1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="N1" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>8</v>
@@ -1563,662 +2238,862 @@
         <v>9</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="G2" s="4"/>
+        <v>56</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>54</v>
+      </c>
       <c r="H2" s="4"/>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="1"/>
+        <v>62</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>63</v>
+      </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>66</v>
+      </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="E5" s="1"/>
+        <v>60</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>68</v>
+      </c>
       <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
+      <c r="G5" s="4" t="s">
+        <v>54</v>
+      </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14" ht="58" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="1"/>
+        <v>69</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>74</v>
+      </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
+      <c r="H6" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="1"/>
+        <v>70</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>75</v>
+      </c>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E8" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="1"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
+      <c r="I8" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" ht="87" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9" s="1"/>
+        <v>79</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>88</v>
+      </c>
       <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
+      <c r="G9" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>71</v>
+      </c>
       <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
+        <v>83</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>87</v>
+      </c>
       <c r="I10" s="1"/>
+      <c r="J10" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E11" s="1"/>
+        <v>82</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>89</v>
+      </c>
       <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
+      <c r="G11" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>81</v>
+      </c>
       <c r="I11" s="1"/>
+      <c r="J11" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14" ht="116" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E12" s="1"/>
+        <v>91</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>97</v>
+      </c>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
+      <c r="J12" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E13" s="1"/>
+        <v>96</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>98</v>
+      </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14" ht="246.5" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E14" s="1"/>
+        <v>90</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>99</v>
+      </c>
       <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
+      <c r="G14" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>71</v>
+      </c>
       <c r="I14" s="1"/>
+      <c r="J14" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14" ht="188.5" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E15" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>105</v>
+      </c>
       <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
+      <c r="G15" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>81</v>
+      </c>
       <c r="I15" s="1"/>
+      <c r="J15" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A16" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
+    <row r="16" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="10"/>
+      <c r="J16" s="10"/>
+      <c r="K16" s="10"/>
+      <c r="L16" s="10"/>
+      <c r="M16" s="10"/>
+      <c r="N16" s="10" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A17" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
+    <row r="17" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="F17" s="10"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="10"/>
+      <c r="J17" s="10"/>
+      <c r="K17" s="10"/>
+      <c r="L17" s="10"/>
+      <c r="M17" s="10"/>
+      <c r="N17" s="10" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A18" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
+    <row r="18" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="F18" s="10"/>
+      <c r="G18" s="10"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="10"/>
+      <c r="J18" s="10"/>
+      <c r="K18" s="10"/>
+      <c r="L18" s="10"/>
+      <c r="M18" s="10"/>
+      <c r="N18" s="10" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A19" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
+    <row r="19" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="F19" s="10"/>
+      <c r="G19" s="10"/>
+      <c r="H19" s="10"/>
+      <c r="I19" s="10"/>
+      <c r="J19" s="10"/>
+      <c r="K19" s="10"/>
+      <c r="L19" s="10"/>
+      <c r="M19" s="10"/>
+      <c r="N19" s="10" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A20" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
+    <row r="20" spans="1:14" s="12" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A20" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="F20" s="10"/>
+      <c r="G20" s="10"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="J20" s="10"/>
+      <c r="K20" s="10"/>
+      <c r="L20" s="10"/>
+      <c r="M20" s="10"/>
+      <c r="N20" s="10" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:14" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E21" s="1"/>
+        <v>27</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>125</v>
+      </c>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
+      <c r="J21" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E22" s="1"/>
+        <v>28</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>111</v>
+      </c>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E23" s="1"/>
+        <v>29</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>114</v>
+      </c>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E24" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>115</v>
+      </c>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E25" s="1"/>
+        <v>116</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>117</v>
+      </c>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
+      <c r="M25" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:14" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E26" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>119</v>
+      </c>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
+      <c r="J26" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="N26" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:14" ht="58" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E27" s="1"/>
+        <v>32</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>120</v>
+      </c>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+      <c r="M27" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="N27" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E28" s="1"/>
+        <v>33</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>122</v>
+      </c>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="N28" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:14" ht="203" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E29" s="1"/>
+        <v>49</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>124</v>
+      </c>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A30" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A31" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A32" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A33" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E33" s="1"/>
-      <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
-      <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A34" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E34" s="1"/>
-      <c r="F34" s="1"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="1"/>
-      <c r="I34" s="1"/>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A35" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A36" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
+      <c r="J29" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="K29" s="1"/>
+      <c r="L29" s="1"/>
+      <c r="M29" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="N29" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="19" type="noConversion"/>

--- a/src/test/resources/testdata/Modules/02_ClaimPoints/ClaimPoints/03_CategoryPageTest.xlsx
+++ b/src/test/resources/testdata/Modules/02_ClaimPoints/ClaimPoints/03_CategoryPageTest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\02_ClaimPoints\ClaimPoints\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAFDC4B0-5AC9-4846-A51A-2A2061B0CFB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA060F9D-8CAE-41A3-82BB-59D74539F832}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D5674106-8292-4F40-9DFC-E6EAC771FC2F}"/>
   </bookViews>
@@ -16,7 +16,6 @@
     <sheet name="TestCases" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -2224,7 +2223,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" ht="145" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>50</v>
       </c>

--- a/src/test/resources/testdata/Modules/02_ClaimPoints/ClaimPoints/03_CategoryPageTest.xlsx
+++ b/src/test/resources/testdata/Modules/02_ClaimPoints/ClaimPoints/03_CategoryPageTest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\02_ClaimPoints\ClaimPoints\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA060F9D-8CAE-41A3-82BB-59D74539F832}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9E95F1F-1C81-4096-8750-027E111554A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D5674106-8292-4F40-9DFC-E6EAC771FC2F}"/>
   </bookViews>
@@ -1373,7 +1373,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1562,6 +1562,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1766,7 +1772,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1788,6 +1794,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="35" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2501,7 +2508,7 @@
       </c>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
-      <c r="M10" s="1" t="s">
+      <c r="M10" s="13" t="s">
         <v>86</v>
       </c>
       <c r="N10" s="1" t="s">

--- a/src/test/resources/testdata/Modules/02_ClaimPoints/ClaimPoints/03_CategoryPageTest.xlsx
+++ b/src/test/resources/testdata/Modules/02_ClaimPoints/ClaimPoints/03_CategoryPageTest.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\02_ClaimPoints\ClaimPoints\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9E95F1F-1C81-4096-8750-027E111554A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF7A3D61-62D3-4C9B-B90B-A2EA8BF87764}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D5674106-8292-4F40-9DFC-E6EAC771FC2F}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="128">
   <si>
     <t>TESTCASE_ID</t>
   </si>
@@ -744,9 +744,6 @@
     <t>Cement</t>
   </si>
   <si>
-    <t>Ambuja Cement</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">Verify </t>
     </r>
@@ -1057,25 +1054,6 @@
   </si>
   <si>
     <t>verify_cartdetails_added_categoryname
-cartdetails_clickon_cancelbtn
-cartdetails_clickon_alertbox_yesbtn</t>
-  </si>
-  <si>
-    <t>category_clickon_refreshbtn
-category_selectcategory
-category_selectbrand
-category_enterqty
-hidekeyboard
-category_enter_productremark
-hidekeyboard
-category_clickon_addtocart_btn
-category_enterqty
-hidekeyboard
-category_enter_productremark
-hidekeyboard
-category_clickon_addtocart_btn
-category_clickon_carticon
-verify_cartdetails_productcount
 cartdetails_clickon_cancelbtn
 cartdetails_clickon_alertbox_yesbtn</t>
   </si>
@@ -1114,9 +1092,6 @@
   </si>
   <si>
     <t>verify_cartdetails_qty</t>
-  </si>
-  <si>
-    <t>Ambj001:12,Ambo002:10</t>
   </si>
   <si>
     <t>cartdetails_clickon_cancelbtn
@@ -1212,6 +1187,34 @@
   </si>
   <si>
     <t>10</t>
+  </si>
+  <si>
+    <t>APPIUM Panther</t>
+  </si>
+  <si>
+    <t>APPIUM CEMENT</t>
+  </si>
+  <si>
+    <t>APMCMT0001:12,APMCMT0002:10</t>
+  </si>
+  <si>
+    <t>category_clickon_refreshbtn
+category_selectcategory
+category_selectbrand
+category_enterqty
+hidekeyboard
+category_enter_productremark
+hidekeyboard
+category_clickon_addtocart_btn
+category_enterqty
+hidekeyboard
+category_enter_productremark2
+hidekeyboard
+category_clickon_addtocart_btn
+category_clickon_carticon
+verify_cartdetails_productcount
+cartdetails_clickon_cancelbtn
+cartdetails_clickon_alertbox_yesbtn</t>
   </si>
 </sst>
 </file>
@@ -2174,16 +2177,21 @@
   <dimension ref="A1:N29"/>
   <sheetFormatPr defaultColWidth="12.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="12.1796875" style="2"/>
+    <col min="1" max="1" width="20.90625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.7265625" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.1796875" style="2"/>
-    <col min="5" max="5" width="50.08984375" style="2" customWidth="1"/>
-    <col min="6" max="7" width="12.1796875" style="2"/>
-    <col min="8" max="8" width="13.81640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.453125" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="12.1796875" style="2"/>
+    <col min="4" max="4" width="73.08984375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="38.08984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.6328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.6328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="29.453125" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.08984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.81640625" style="2" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="17.08984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="12.1796875" style="2"/>
+    <col min="13" max="13" width="29.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.08984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="12.1796875" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.35">
@@ -2221,7 +2229,7 @@
         <v>59</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="M1" s="7" t="s">
         <v>2</v>
@@ -2466,14 +2474,14 @@
         <v>79</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="4" t="s">
         <v>54</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>71</v>
+        <v>124</v>
       </c>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
@@ -2497,19 +2505,19 @@
         <v>18</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I10" s="1"/>
       <c r="J10" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="13" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="N10" s="1" t="s">
         <v>5</v>
@@ -2526,21 +2534,21 @@
         <v>19</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F11" s="1"/>
       <c r="G11" s="1" t="s">
         <v>80</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>81</v>
+        <v>125</v>
       </c>
       <c r="I11" s="1"/>
       <c r="J11" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
@@ -2560,22 +2568,22 @@
         <v>20</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N12" s="1" t="s">
         <v>5</v>
@@ -2592,10 +2600,10 @@
         <v>21</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
@@ -2622,28 +2630,28 @@
         <v>22</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>99</v>
+        <v>127</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="4" t="s">
         <v>54</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>71</v>
+        <v>124</v>
       </c>
       <c r="I14" s="1"/>
       <c r="J14" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="K14" s="1"/>
       <c r="L14" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N14" s="1" t="s">
         <v>5</v>
@@ -2663,18 +2671,18 @@
         <v>26</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1" t="s">
         <v>80</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>81</v>
+        <v>125</v>
       </c>
       <c r="I15" s="1"/>
       <c r="J15" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
@@ -2694,10 +2702,10 @@
         <v>35</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F16" s="10"/>
       <c r="G16" s="10"/>
@@ -2722,10 +2730,10 @@
         <v>36</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F17" s="10"/>
       <c r="G17" s="10"/>
@@ -2753,7 +2761,7 @@
         <v>25</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F18" s="10"/>
       <c r="G18" s="10"/>
@@ -2781,7 +2789,7 @@
         <v>23</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F19" s="10"/>
       <c r="G19" s="10"/>
@@ -2809,13 +2817,13 @@
         <v>24</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F20" s="10"/>
       <c r="G20" s="10"/>
       <c r="H20" s="10"/>
       <c r="I20" s="10" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="J20" s="10"/>
       <c r="K20" s="10"/>
@@ -2839,14 +2847,14 @@
         <v>27</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
@@ -2871,7 +2879,7 @@
         <v>28</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
@@ -2901,7 +2909,7 @@
         <v>29</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
@@ -2911,7 +2919,7 @@
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
       <c r="M23" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="N23" s="1" t="s">
         <v>5</v>
@@ -2931,7 +2939,7 @@
         <v>30</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
@@ -2941,7 +2949,7 @@
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
       <c r="M24" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="N24" s="1" t="s">
         <v>5</v>
@@ -2958,10 +2966,10 @@
         <v>44</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
@@ -2971,7 +2979,7 @@
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
       <c r="M25" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="N25" s="1" t="s">
         <v>5</v>
@@ -2991,19 +2999,19 @@
         <v>31</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="N26" s="1" t="s">
         <v>5</v>
@@ -3023,7 +3031,7 @@
         <v>32</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
@@ -3033,7 +3041,7 @@
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
       <c r="M27" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="N27" s="1" t="s">
         <v>5</v>
@@ -3053,7 +3061,7 @@
         <v>33</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
@@ -3083,19 +3091,19 @@
         <v>49</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="N29" s="1" t="s">
         <v>5</v>

--- a/src/test/resources/testdata/Modules/02_ClaimPoints/ClaimPoints/03_CategoryPageTest.xlsx
+++ b/src/test/resources/testdata/Modules/02_ClaimPoints/ClaimPoints/03_CategoryPageTest.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\02_ClaimPoints\ClaimPoints\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF7A3D61-62D3-4C9B-B90B-A2EA8BF87764}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC32FA05-ED7E-483E-BC44-E07F6E4A0CC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D5674106-8292-4F40-9DFC-E6EAC771FC2F}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="127">
   <si>
     <t>TESTCASE_ID</t>
   </si>
@@ -619,9 +619,6 @@
     </r>
   </si>
   <si>
-    <t>Jindal Panther</t>
-  </si>
-  <si>
     <t>roundds</t>
   </si>
   <si>
@@ -689,9 +686,6 @@
     <t>category_enterproductname_insearchfield
 hidekeyboard
 verify_category_productcode_inlist</t>
-  </si>
-  <si>
-    <t>PROD005</t>
   </si>
   <si>
     <r>
@@ -1215,6 +1209,9 @@
 verify_cartdetails_productcount
 cartdetails_clickon_cancelbtn
 cartdetails_clickon_alertbox_yesbtn</t>
+  </si>
+  <si>
+    <t>APMTMT0002</t>
   </si>
 </sst>
 </file>
@@ -2229,7 +2226,7 @@
         <v>59</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="M1" s="7" t="s">
         <v>2</v>
@@ -2378,21 +2375,21 @@
         <v>69</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
       <c r="H6" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="I6" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>72</v>
       </c>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N6" s="1" t="s">
         <v>5</v>
@@ -2412,7 +2409,7 @@
         <v>70</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
@@ -2439,22 +2436,22 @@
         <v>16</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E8" s="9" t="s">
         <v>76</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>77</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1" t="s">
-        <v>78</v>
+        <v>126</v>
       </c>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1" t="s">
-        <v>78</v>
+        <v>126</v>
       </c>
       <c r="N8" s="1" t="s">
         <v>5</v>
@@ -2471,17 +2468,17 @@
         <v>17</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="4" t="s">
         <v>54</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
@@ -2505,19 +2502,19 @@
         <v>18</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="I10" s="1"/>
       <c r="J10" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="13" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="N10" s="1" t="s">
         <v>5</v>
@@ -2534,21 +2531,21 @@
         <v>19</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F11" s="1"/>
       <c r="G11" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I11" s="1"/>
       <c r="J11" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
@@ -2568,22 +2565,22 @@
         <v>20</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="N12" s="1" t="s">
         <v>5</v>
@@ -2600,10 +2597,10 @@
         <v>21</v>
       </c>
       <c r="D13" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E13" s="9" t="s">
         <v>95</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>97</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
@@ -2613,7 +2610,7 @@
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="N13" s="1" t="s">
         <v>5</v>
@@ -2630,28 +2627,28 @@
         <v>22</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="4" t="s">
         <v>54</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="I14" s="1"/>
       <c r="J14" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="K14" s="1"/>
       <c r="L14" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="N14" s="1" t="s">
         <v>5</v>
@@ -2671,18 +2668,18 @@
         <v>26</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I15" s="1"/>
       <c r="J15" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
@@ -2702,10 +2699,10 @@
         <v>35</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F16" s="10"/>
       <c r="G16" s="10"/>
@@ -2730,10 +2727,10 @@
         <v>36</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F17" s="10"/>
       <c r="G17" s="10"/>
@@ -2761,7 +2758,7 @@
         <v>25</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F18" s="10"/>
       <c r="G18" s="10"/>
@@ -2789,7 +2786,7 @@
         <v>23</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F19" s="10"/>
       <c r="G19" s="10"/>
@@ -2817,13 +2814,13 @@
         <v>24</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F20" s="10"/>
       <c r="G20" s="10"/>
       <c r="H20" s="10"/>
       <c r="I20" s="10" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="J20" s="10"/>
       <c r="K20" s="10"/>
@@ -2847,14 +2844,14 @@
         <v>27</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
@@ -2879,7 +2876,7 @@
         <v>28</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
@@ -2909,7 +2906,7 @@
         <v>29</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
@@ -2919,7 +2916,7 @@
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
       <c r="M23" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="N23" s="1" t="s">
         <v>5</v>
@@ -2939,7 +2936,7 @@
         <v>30</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
@@ -2949,7 +2946,7 @@
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
       <c r="M24" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="N24" s="1" t="s">
         <v>5</v>
@@ -2966,10 +2963,10 @@
         <v>44</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
@@ -2979,7 +2976,7 @@
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
       <c r="M25" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="N25" s="1" t="s">
         <v>5</v>
@@ -2999,19 +2996,19 @@
         <v>31</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="N26" s="1" t="s">
         <v>5</v>
@@ -3031,7 +3028,7 @@
         <v>32</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
@@ -3041,7 +3038,7 @@
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
       <c r="M27" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="N27" s="1" t="s">
         <v>5</v>
@@ -3061,7 +3058,7 @@
         <v>33</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
@@ -3091,19 +3088,19 @@
         <v>49</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="N29" s="1" t="s">
         <v>5</v>
